--- a/file_upload_forms/020_mechanical_coupling_application_form--file_upload_forms.xlsx
+++ b/file_upload_forms/020_mechanical_coupling_application_form--file_upload_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -510,15 +510,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mechanical_coupling_app_form_1</t>
+          <t>requester_information</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Requester</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Requester Information</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please provide your name and email address.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -533,15 +537,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mechanical_coupling_app_form_2</t>
+          <t>request_details</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Requester</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Request Details</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please provide a detailed description of your request.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -556,15 +564,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mechanical_coupling_app_form_3</t>
+          <t>request_time</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Request Time</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please select the time of your request.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -579,15 +591,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mechanical_coupling_app_form_4</t>
+          <t>supporting_documents</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Supporting Documents</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Upload any documents that support your request.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -602,246 +618,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mechanical_coupling_app_form_5</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>mechanical_coupling_app_form_6</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Request Date</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mechanical_coupling_app_form_7</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Request Time</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>mechanical_coupling_app_form_8</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Requester Email</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>mechanical_coupling_app_form_9</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Requester Phone</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>mechanical_coupling_app_form_10</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Requester Phone</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>mechanical_coupling_app_form_11</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Requester Phone</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>mechanical_coupling_app_form_12</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Requester Phone</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>mechanical_coupling_app_form_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Requester Phone</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>mechanical_coupling_app_form_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Requester Phone</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>mechanical_coupling_app_form_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Requester Phone</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
